--- a/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
@@ -2732,11 +2732,6 @@
           <t>CIB</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2754,10 +2749,6 @@
           <t>Markets and Securities Services</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2780,9 +2771,6 @@
           <t>Markets</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2810,7 +2798,6 @@
           <t>Foreign Exchange</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
           <t>Foreign Exchange|FX</t>
@@ -2843,7 +2830,6 @@
           <t>Rates</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
           <t>Rates</t>
@@ -2876,7 +2862,6 @@
           <t>Credit</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
           <t>Credit Trading</t>
@@ -2909,7 +2894,6 @@
           <t>Equities</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
           <t>Equities</t>
@@ -2937,9 +2921,6 @@
           <t>Securities Services</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2967,7 +2948,6 @@
           <t>Custody</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
           <t>Custody</t>
@@ -3000,7 +2980,6 @@
           <t>Fund Administration</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
           <t>Fund Administration</t>
@@ -3033,7 +3012,6 @@
           <t>Issuer Services</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
           <t>Issuer Services</t>
@@ -3056,10 +3034,6 @@
           <t>Global Payments Solutions</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3082,8 +3056,6 @@
           <t>Payments and Cash Management</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
           <t>Payments and Cash Management|PCM</t>
@@ -3111,8 +3083,6 @@
           <t>Liquidity Management</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
           <t>Liquidity Management</t>
@@ -3140,8 +3110,6 @@
           <t>Commercial Cards</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
           <t>Commercial Cards</t>
@@ -3164,10 +3132,6 @@
           <t>Global Trade Solutions</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3190,8 +3154,6 @@
           <t>Documentary Trade</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
           <t>Documentary Trade</t>
@@ -3219,8 +3181,6 @@
           <t>Receivables Finance</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
           <t>Receivables Finance</t>
@@ -3248,8 +3208,6 @@
           <t>Guarantees</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
           <t>Guarantees</t>
@@ -3272,10 +3230,6 @@
           <t>Credit and Lending</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3298,8 +3252,6 @@
           <t>Corporate Lending</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
           <t>Corporate Lending</t>
@@ -3327,8 +3279,6 @@
           <t>Structured Finance</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
           <t>Structured Finance</t>
@@ -3356,8 +3306,6 @@
           <t>Portfolio Management</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
           <t>Portfolio Management</t>
@@ -3380,10 +3328,6 @@
           <t>Capital Markets and Advisory</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3406,8 +3350,6 @@
           <t>Debt Capital Markets</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
           <t>Debt Capital Markets|DCM</t>
@@ -3435,8 +3377,6 @@
           <t>Equity Capital Markets</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
           <t>Equity Capital Markets|ECM</t>
@@ -3464,8 +3404,6 @@
           <t>Advisory</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
           <t>Advisory</t>
@@ -3488,9 +3426,6 @@
           <t>HIF</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
           <t>HIF</t>
@@ -3513,9 +3448,6 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
           <t>Other</t>
@@ -3533,10 +3465,6 @@
           <t>Non product aligned</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr"/>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
           <t>Non product aligned</t>
@@ -4113,11 +4041,6 @@
           <t>PBT (Reported)</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4135,10 +4058,6 @@
           <t>PBT (ex Notables)</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4161,9 +4080,6 @@
           <t>Total Revenue (ex Notables)</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4191,7 +4107,6 @@
           <t>MSS</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>MSS</t>
@@ -4224,8 +4139,6 @@
           <t>Credit and Lending</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4327,7 +4240,6 @@
           <t>Global Trade Solutions</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>Global Trade Solutions|GTS</t>
@@ -4360,7 +4272,6 @@
           <t>HIF</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>HIF</t>
@@ -4393,7 +4304,6 @@
           <t>Global Payments Solutions</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>Global Payments Solutions|GPS</t>
@@ -4426,7 +4336,6 @@
           <t>CMA Net</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>CMA Net</t>
@@ -4459,7 +4368,6 @@
           <t>Other Revenue</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
           <t>Other Revenue</t>
@@ -4487,8 +4395,6 @@
           <t>ECLs (ex Notables)</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
           <t>ECLs (ex Notables)|ECL (ex Notables)</t>
@@ -4516,9 +4422,6 @@
           <t>Total Operating Expenses (ex Notables)</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4546,8 +4449,6 @@
           <t>Direct Costs (ex VP)</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4649,7 +4550,6 @@
           <t>Variable Pay (VP)</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
           <t>Variable Pay (VP)|Variable Pay</t>
@@ -4682,7 +4582,6 @@
           <t>Indirect Costs</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
           <t>Indirect Costs</t>
@@ -4705,10 +4604,6 @@
           <t>Notables</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4731,8 +4626,6 @@
           <t>Revenue Notables</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
           <t>Revenue Notables</t>
@@ -4760,8 +4653,6 @@
           <t>Opex Notables</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
           <t>Opex Notables</t>
@@ -4779,11 +4670,6 @@
           <t>Customers and Banks Deposits (PE)</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4801,9 +4687,6 @@
           <t>o/w Customer Deposits (PE)</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
           <t>Customer Deposits (PE)</t>
@@ -4826,9 +4709,6 @@
           <t>o/w Bank Deposits (PE)</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
           <t>Bank Deposits (PE)</t>
@@ -4846,11 +4726,6 @@
           <t>Loans and Advances to Customers and Banks (PE)</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4868,9 +4743,6 @@
           <t>o/w Loans and Advances to Customers (PE)</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
           <t>Loans and Advances to Customers (PE)</t>
@@ -4893,9 +4765,6 @@
           <t>o/w Loans and Advances to Banks (PE)</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
           <t>Loans and Advances to Banks (PE)</t>
@@ -4913,10 +4782,6 @@
           <t>Total RWAs</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
           <t>Total RWAs|RWAs</t>
@@ -4934,10 +4799,6 @@
           <t>Headcount</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
           <t>Headcount|FTE</t>
@@ -4955,10 +4816,6 @@
           <t>Reported RoTE (%)</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
           <t>Reported RoTE (%)|RoTE</t>
@@ -4976,10 +4833,6 @@
           <t>CER ex Notables (%)</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
           <t>CER ex Notables (%)|CER</t>
@@ -4997,10 +4850,6 @@
           <t>ECLs / Loans and Advances (%)</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
           <t>ECLs / Loans and Advances (%)</t>
@@ -6401,8 +6250,6 @@
           <t>Global</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -7181,7 +7028,6 @@
           <t>Holdings</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7197,9 +7043,9 @@
   <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="100" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="105" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7215,7 +7061,7 @@
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>Pattern</t>
+          <t>Commentary (written as you would write it — the pattern is detected automatically)</t>
         </is>
       </c>
     </row>
@@ -7232,7 +7078,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{line} {var} {vs} across the Group, led by {drivers}.</t>
+          <t>PBT was up $68m (4.2%) vs the YTD target across the Group, led by Wealth and Personal Banking.</t>
         </is>
       </c>
     </row>
@@ -7249,7 +7095,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{scope}: {line} {var} {vs}, led by {drivers}.</t>
+          <t>IWPB: Revenue was up $102m (2.5%) vs Q2 2025, led by Mutual Funds and Deposits.</t>
         </is>
       </c>
     </row>
@@ -7266,7 +7112,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{scope}: {line} {var} {vs} across the region, driven by {drivers}.</t>
+          <t>Asia: Revenue was up $45m (3.1%) vs Q2 2025 across the region, driven by Singapore and Hong Kong.</t>
         </is>
       </c>
     </row>
@@ -7283,91 +7129,95 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>In {scope}, {line} came in at {main}, {var} {vs} on {drivers}.</t>
+          <t>In Singapore, Revenue came in at $643m, up $28m (4.5%) vs target on the back of Mutual Funds.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Exec brief</t>
+          <t>CIB Global</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CIB Global</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{line} {var} {vs}, led by {drivers}.</t>
+          <t>CIB: Revenue was up $45m (4.7%) vs Q2 2025, led by Payments and Trade.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FP&amp;A detail</t>
+          <t>CIB Regional</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CIB Regional</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{line}: {main} against {base} — {varamt} ({varpct}) {vs}. Key movers: {drivers}.</t>
+          <t>Asia: Revenue was up $21m (2.9%) vs Q2 2025 across the region, driven by Hong Kong and Singapore.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>&lt;i&gt;Scope words: Group · Global · Regional · Country, optionally led by a business (IWPB Global) or a place (Singapore). With the style set to Auto — match the scope, the page adopts the best-fitting template as the scope moves; no scoped template defined for a scope means the pack narrative speaks there. A blank scope makes a named style picked by hand.</t>
+          <t>CIB Country</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CIB Country</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>In Singapore, Revenue came in at $321m, up $12m (3.8%) vs target on the back of Payments.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CIB Global</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>CIB Global</t>
-        </is>
-      </c>
+          <t>Exec brief</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{scope}: {line} {var} {vs}, led by {drivers}.</t>
+          <t>Revenue was up $102m (2.5%) vs Q2 2025, led by Mutual Funds.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CIB Regional</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>CIB Regional</t>
-        </is>
-      </c>
+          <t>FP&amp;A detail</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{scope}: {line} {var} {vs} across the region, driven by {drivers}.</t>
+          <t>Revenue: $4,193m against $4,091m — up $102m (2.5%) vs Q2 2025. Key movers: Mutual Funds.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CIB Country</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>CIB Country</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>In {scope}, {line} came in at {main}, {var} {vs} on {drivers}.</t>
-        </is>
-      </c>
+          <t>&lt;i&gt;Write each row as a real commentary sentence — the page detects where the figures sit and turns it into the pattern itself; the example numbers never survive into the output. Scope words: Group · Global · Regional · Country, optionally led by a business or a place. A row may also carry a token pattern directly. A tab named "Template &lt;scope&gt;" holding a longer write-up overrides the row for the same scope.</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9268,7 +9118,6 @@
           <t>Summary</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>June closes the half ahead of plan on revenue and behind on costs.</t>
@@ -9276,7 +9125,6 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
           <t>Global Payments Solutions</t>

--- a/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
@@ -8,18 +8,19 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calculations" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TilePriority" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dimensions" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Views" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Labels" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Drivers" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metrics" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commentary" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ProductHierarchy" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AccountHierarchy" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CountryHierarchy" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CommentaryTemplates" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiles" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calculations" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TilePriority" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dimensions" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Views" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Labels" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Drivers" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metrics" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commentary" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ProductHierarchy" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AccountHierarchy" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CountryHierarchy" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CommentaryTemplates" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1423,6 +1424,173 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NII carried the half. Deposit margin held better than the plan assumed as the pass-through on time deposits was slower than expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Net Fee Income was the softer line. Investment activity thinned after the March rally and brokerage volumes have not come back, though the recurring wealth fee base is unchanged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Deposits ended the half broadly flat. The migration from current accounts into time deposits continued at much the same pace as the first quarter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Loans grew on mortgage completions that had been sitting in the pipeline since February.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Cards spend was seasonally strong in June but the balance build is behind where the plan had it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Insurance new business held up against a soft market, helped by the bancassurance push in the second quarter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Trading Income was flat and is not expected to move materially in the second half.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>The half closed ahead of plan on revenue, with costs the watch item into the second half.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Financial Summary</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Rates and FX carried the half; deposit margin narrowed broadly as planned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Markets and Securities Services</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Rates and FX led the half while Custody stayed soft.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Global Trade Solutions</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Drawdowns slipped into July - timing, not demand. The pipeline is intact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>June closes the half ahead of plan on revenue and behind on costs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Global Payments Solutions</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Payments volumes held up well; liquidity margin thinner as rates came off.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3476,7 +3644,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4861,7 +5029,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7034,7 +7202,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7190,7 +7358,6 @@
           <t>Exec brief</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>Revenue was up $102m (2.5%) vs Q2 2025, led by Mutual Funds.</t>
@@ -7203,7 +7370,6 @@
           <t>FP&amp;A detail</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>Revenue: $4,193m against $4,091m — up $102m (2.5%) vs Q2 2025. Key movers: Mutual Funds.</t>
@@ -7216,8 +7382,6 @@
           <t>&lt;i&gt;Write each row as a real commentary sentence — the page detects where the figures sit and turns it into the pattern itself; the example numbers never survive into the output. Scope words: Group · Global · Regional · Country, optionally led by a business or a place. A row may also carry a token pattern directly. A tab named "Template &lt;scope&gt;" holding a longer write-up overrides the row for the same scope.</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7225,6 +7389,44 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Tile</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Show</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>&lt;One row per tile. Column A: the tile name exactly as it reads on the Summary (its MICA Level 2 / line name) — or a pattern like cost.* for a family. Column B: Y to show, N to hide. Hidden tiles stay one click away behind "Show parked tiles". If every row here says Y, ONLY those tiles show and the rest are parked. Delete all rows to show everything.</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7345,7 +7547,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7459,7 +7661,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8062,7 +8264,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8188,7 +8390,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8542,7 +8744,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8572,7 +8774,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8972,171 +9174,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Line</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Text</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>NII carried the half. Deposit margin held better than the plan assumed as the pass-through on time deposits was slower than expected.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Net Fee Income was the softer line. Investment activity thinned after the March rally and brokerage volumes have not come back, though the recurring wealth fee base is unchanged.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Deposits ended the half broadly flat. The migration from current accounts into time deposits continued at much the same pace as the first quarter.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Loans grew on mortgage completions that had been sitting in the pipeline since February.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Cards spend was seasonally strong in June but the balance build is behind where the plan had it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Insurance new business held up against a soft market, helped by the bancassurance push in the second quarter.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Trading Income was flat and is not expected to move materially in the second half.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>The half closed ahead of plan on revenue, with costs the watch item into the second half.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Financial Summary</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Rates and FX carried the half; deposit margin narrowed broadly as planned.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Markets and Securities Services</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Rates and FX led the half while Custody stayed soft.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Global Trade Solutions</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Drawdowns slipped into July - timing, not demand. The pipeline is intact.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Summary</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>June closes the half ahead of plan on revenue and behind on costs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Global Payments Solutions</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Payments volumes held up well; liquidity margin thinner as rates came off.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
@@ -7419,7 +7419,6 @@
           <t>&lt;One row per tile. Column A: the tile name exactly as it reads on the Summary (its MICA Level 2 / line name) — or a pattern like cost.* for a family. Column B: Y to show, N to hide. Hidden tiles stay one click away behind "Show parked tiles". If every row here says Y, ONLY those tiles show and the rest are parked. Delete all rows to show everything.</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8780,7 +8779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -9030,142 +9029,118 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Banking NII</t>
+          <t>Fee and other income</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>income=Banking NII</t>
+          <t>income=Fee and other income</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Fee and other income</t>
+          <t>ECLs (ex Notables)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>income=Fee and other income</t>
+          <t>accH3=ECLs (ex Notables)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ECLs (ex Notables)</t>
+          <t>Direct Costs (ex VP)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>accH3=ECLs (ex Notables)</t>
+          <t>accH4=Direct Costs (ex VP)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Direct Costs (ex VP)</t>
+          <t>Variable Pay (VP)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>accH4=Direct Costs (ex VP)</t>
+          <t>accH4=Variable Pay (VP)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Variable Pay (VP)</t>
+          <t>Total Operating Expenses (ex Notables)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>accH4=Variable Pay (VP)</t>
+          <t>accH3=Total Operating Expenses (ex Notables)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Indirect Costs</t>
+          <t>PBT (ex Notables)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>accH4=Indirect Costs</t>
+          <t>accH2=PBT (ex Notables)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Total Operating Expenses (ex Notables)</t>
+          <t>PBT (Reported)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>accH3=Total Operating Expenses (ex Notables)</t>
+          <t>accH1=PBT (Reported)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PBT (ex Notables)</t>
+          <t>Customer Deposits (PE)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>accH2=PBT (ex Notables)</t>
+          <t>accH2=o/w Customer Deposits (PE)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PBT (Reported)</t>
+          <t>Loans and Advances to Customers (PE)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>accH1=PBT (Reported)</t>
+          <t>accH2=o/w Loans and Advances to Customers (PE)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Customer Deposits (PE)</t>
+          <t>Total RWAs</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
-        <is>
-          <t>accH2=o/w Customer Deposits (PE)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Loans and Advances to Customers (PE)</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>accH2=o/w Loans and Advances to Customers (PE)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Total RWAs</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
         <is>
           <t>accH1=Total RWAs</t>
         </is>

--- a/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
@@ -745,7 +745,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>cost|\becl\b|expected\s+credit|impair|expense</t>
+          <t>cost|\becls?\b|expected\s+credit|impair|expense|\boffsets?\b|contra</t>
         </is>
       </c>
     </row>

--- a/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B88"/>
+  <dimension ref="A1:B91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1410,6 +1410,38 @@
       <c r="A88" t="inlineStr">
         <is>
           <t>tile_visible</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>tile_net</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>tile_net_auto</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>revenue_patterns</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>revenue|income|\bfees?\b|\bnii\b|turnover|\bnnii\b</t>
         </is>
       </c>
     </row>
@@ -7394,7 +7426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -7412,11 +7444,16 @@
           <t>Show</t>
         </is>
       </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Nets with</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>&lt;One row per tile. Column A: the tile name exactly as it reads on the Summary (its MICA Level 2 / line name) — or a pattern like cost.* for a family. Column B: Y to show, N to hide. Hidden tiles stay one click away behind "Show parked tiles". If every row here says Y, ONLY those tiles show and the rest are parked. Delete all rows to show everything.</t>
+          <t>One row per tile. Column A: the tile name exactly as it reads on the Summary (its MICA Level 2 / line name) — or a pattern like cost.* for a family. Column B: Y to show, N to hide. Hidden tiles stay one click away behind "Show parked tiles". If every row here says Y, ONLY those tiles show and the rest are parked. Column C (optional): the line or lines this tile nets in — e.g. Revenue nets with "Other Revenue, Revenue offsets", so the tile shows the net figure. Put "-" to stop a netting the page would otherwise make. Delete all rows to show everything.</t>
         </is>
       </c>
     </row>

--- a/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
@@ -654,7 +654,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>level2</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,6 @@
           <t>tile_net</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">

--- a/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
@@ -14,13 +14,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dimensions" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Views" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Labels" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Drivers" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metrics" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commentary" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ProductHierarchy" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AccountHierarchy" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CountryHierarchy" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CommentaryTemplates" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metrics" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commentary" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ProductHierarchy" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AccountHierarchy" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CountryHierarchy" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CommentaryTemplates" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1455,173 +1454,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Line</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Text</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>NII carried the half. Deposit margin held better than the plan assumed as the pass-through on time deposits was slower than expected.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Net Fee Income was the softer line. Investment activity thinned after the March rally and brokerage volumes have not come back, though the recurring wealth fee base is unchanged.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Deposits ended the half broadly flat. The migration from current accounts into time deposits continued at much the same pace as the first quarter.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Loans grew on mortgage completions that had been sitting in the pipeline since February.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Cards spend was seasonally strong in June but the balance build is behind where the plan had it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Insurance new business held up against a soft market, helped by the bancassurance push in the second quarter.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Trading Income was flat and is not expected to move materially in the second half.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>The half closed ahead of plan on revenue, with costs the watch item into the second half.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Financial Summary</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Rates and FX carried the half; deposit margin narrowed broadly as planned.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Markets and Securities Services</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Rates and FX led the half while Custody stayed soft.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Global Trade Solutions</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Drawdowns slipped into July - timing, not demand. The pipeline is intact.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Summary</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>June closes the half ahead of plan on revenue and behind on costs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Global Payments Solutions</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Payments volumes held up well; liquidity margin thinner as rates came off.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3675,7 +3507,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5060,7 +4892,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7233,7 +7065,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8785,7 +8617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -8800,7 +8632,355 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Driver note</t>
+          <t>Scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>accH2=Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Banking NII</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>accH3=Banking NII</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Fees and Other Income</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>accH3=Fees and Other Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PBT</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>accH1=PBT ex Notables</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Direct Cost ex VP, CC, GT</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>accH3=Direct Cost ex VP, CC, GT</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Variable Pay ex CC</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>accH3=Variable Pay ex CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Indirect Costs</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>accH3=Indirect Costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Operating Expenses</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>accH2=Operating Expenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ECL</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>accH2=ECLs</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Deposits</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>accH2=Deposits</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Loans and Advances</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>accH2=Loans and Advances</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Total Revenue (ex Notables)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>accH3=Total Revenue (ex Notables)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>MSS</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>accH4=MSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Global Payments Solutions</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>accH4=Global Payments Solutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Credit and Lending</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>accH4=Credit and Lending</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Global Trade Solutions</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>accH4=Global Trade Solutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>HIF</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>accH4=HIF</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CMA Net</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>accH4=CMA Net</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Other Revenue</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>accH4=Other Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Fee and other income</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>income=Fee and other income</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ECLs (ex Notables)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>accH3=ECLs (ex Notables)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Direct Costs (ex VP)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>accH4=Direct Costs (ex VP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Variable Pay (VP)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>accH4=Variable Pay (VP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Total Operating Expenses (ex Notables)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>accH3=Total Operating Expenses (ex Notables)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PBT (ex Notables)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>accH2=PBT (ex Notables)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>PBT (Reported)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>accH1=PBT (Reported)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Customer Deposits (PE)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>accH2=o/w Customer Deposits (PE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Loans and Advances to Customers (PE)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>accH2=o/w Loans and Advances to Customers (PE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Total RWAs</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>accH1=Total RWAs</t>
         </is>
       </c>
     </row>
@@ -8815,370 +8995,159 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Key</t>
+          <t>View</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Scope</t>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Text</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>accH2=Revenue</t>
+          <t>NII carried the half. Deposit margin held better than the plan assumed as the pass-through on time deposits was slower than expected.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Banking NII</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>accH3=Banking NII</t>
+          <t>Net Fee Income was the softer line. Investment activity thinned after the March rally and brokerage volumes have not come back, though the recurring wealth fee base is unchanged.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Fees and Other Income</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>accH3=Fees and Other Income</t>
+          <t>Deposits ended the half broadly flat. The migration from current accounts into time deposits continued at much the same pace as the first quarter.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PBT</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>accH1=PBT ex Notables</t>
+          <t>Loans grew on mortgage completions that had been sitting in the pipeline since February.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Direct Cost ex VP, CC, GT</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>accH3=Direct Cost ex VP, CC, GT</t>
+          <t>Cards spend was seasonally strong in June but the balance build is behind where the plan had it.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Variable Pay ex CC</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>accH3=Variable Pay ex CC</t>
+          <t>Insurance new business held up against a soft market, helped by the bancassurance push in the second quarter.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Indirect Costs</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>accH3=Indirect Costs</t>
+          <t>Trading Income was flat and is not expected to move materially in the second half.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>accH2=Operating Expenses</t>
+          <t>The half closed ahead of plan on revenue, with costs the watch item into the second half.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ECL</t>
+          <t>Financial Summary</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>accH2=ECLs</t>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Rates and FX carried the half; deposit margin narrowed broadly as planned.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Deposits</t>
+          <t>Chart</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>accH2=Deposits</t>
+          <t>Markets and Securities Services</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Rates and FX led the half while Custody stayed soft.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Loans and Advances</t>
+          <t>Chart</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>accH2=Loans and Advances</t>
+          <t>Global Trade Solutions</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Drawdowns slipped into July - timing, not demand. The pipeline is intact.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total Revenue (ex Notables)</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>accH3=Total Revenue (ex Notables)</t>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>June closes the half ahead of plan on revenue and behind on costs.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>MSS</t>
-        </is>
-      </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>accH4=MSS</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
           <t>Global Payments Solutions</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>accH4=Global Payments Solutions</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Credit and Lending</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>accH4=Credit and Lending</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Global Trade Solutions</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>accH4=Global Trade Solutions</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>HIF</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>accH4=HIF</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>CMA Net</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>accH4=CMA Net</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Other Revenue</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>accH4=Other Revenue</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Fee and other income</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>income=Fee and other income</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>ECLs (ex Notables)</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>accH3=ECLs (ex Notables)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Direct Costs (ex VP)</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>accH4=Direct Costs (ex VP)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Variable Pay (VP)</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>accH4=Variable Pay (VP)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Total Operating Expenses (ex Notables)</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>accH3=Total Operating Expenses (ex Notables)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>PBT (ex Notables)</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>accH2=PBT (ex Notables)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>PBT (Reported)</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>accH1=PBT (Reported)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Customer Deposits (PE)</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>accH2=o/w Customer Deposits (PE)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Loans and Advances to Customers (PE)</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>accH2=o/w Loans and Advances to Customers (PE)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Total RWAs</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>accH1=Total RWAs</t>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Payments volumes held up well; liquidity margin thinner as rates came off.</t>
         </is>
       </c>
     </row>

--- a/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
@@ -696,7 +696,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>level2</t>
+          <t>auto</t>
         </is>
       </c>
     </row>

--- a/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
@@ -7257,7 +7257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -7284,9 +7284,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>One row per tile. Column A: the tile name exactly as it reads on the Summary (its MICA Level 2 / line name) — or a pattern like cost.* for a family. Column B: Y to show, N to hide. Hidden tiles stay one click away behind "Show parked tiles". If every row here says Y, ONLY those tiles show and the rest are parked. Column C (optional): the line or lines this tile nets in — e.g. Revenue nets with "Other Revenue, Revenue offsets", so the tile shows the net figure. Put "-" to stop a netting the page would otherwise make. Delete all rows to show everything.</t>
-        </is>
-      </c>
+          <t>One row per tile. Column A: the tile name as it reads on the Summary — or a pattern like cost.* for a family. Column B: Y shows, N hides (hidden tiles stay one click away behind "Show parked tiles"; a tab of only-Y rows shows JUST those), and + ADDS a line the grid does not carry — resolved from the Metrics sheet or any MICA level, so "Banking NII | +" puts Banking NII on the grid without touching the rest. Column C (optional): the line or lines this tile nets in — e.g. Revenue nets with "Other Revenue"; "-" stops a netting the page would otherwise make. Delete all rows to show the default grid.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Banking NII</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
@@ -7299,7 +7299,6 @@
           <t>+</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8669,7 +8668,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>accH3=Banking NII</t>
+          <t>micaL2=Revenue; micaL3!=Net Insurance Revenue</t>
         </is>
       </c>
     </row>

--- a/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
@@ -8629,7 +8629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -8647,6 +8647,11 @@
           <t>Scope</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Applies to</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8671,326 +8676,348 @@
           <t>micaL2=Revenue; micaL3!=Net Insurance Revenue</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Fees and Other Income</t>
+          <t>Banking NII</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>accH3=Fees and Other Income</t>
+          <t>accH3=Banking NII</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CIB</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PBT</t>
+          <t>Fees and Other Income</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>accH1=PBT ex Notables</t>
+          <t>accH3=Fees and Other Income</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Direct Cost ex VP, CC, GT</t>
+          <t>PBT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>accH3=Direct Cost ex VP, CC, GT</t>
+          <t>accH1=PBT ex Notables</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Variable Pay ex CC</t>
+          <t>Direct Cost ex VP, CC, GT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>accH3=Variable Pay ex CC</t>
+          <t>accH3=Direct Cost ex VP, CC, GT</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Indirect Costs</t>
+          <t>Variable Pay ex CC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>accH3=Indirect Costs</t>
+          <t>accH3=Variable Pay ex CC</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Indirect Costs</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>accH2=Operating Expenses</t>
+          <t>accH3=Indirect Costs</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ECL</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>accH2=ECLs</t>
+          <t>accH2=Operating Expenses</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Deposits</t>
+          <t>ECL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>accH2=Deposits</t>
+          <t>accH2=ECLs</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Loans and Advances</t>
+          <t>Deposits</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>accH2=Loans and Advances</t>
+          <t>accH2=Deposits</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total Revenue (ex Notables)</t>
+          <t>Loans and Advances</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>accH3=Total Revenue (ex Notables)</t>
+          <t>accH2=Loans and Advances</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MSS</t>
+          <t>Total Revenue (ex Notables)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>accH4=MSS</t>
+          <t>accH3=Total Revenue (ex Notables)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Global Payments Solutions</t>
+          <t>MSS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>accH4=Global Payments Solutions</t>
+          <t>accH4=MSS</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Credit and Lending</t>
+          <t>Global Payments Solutions</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>accH4=Credit and Lending</t>
+          <t>accH4=Global Payments Solutions</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Global Trade Solutions</t>
+          <t>Credit and Lending</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>accH4=Global Trade Solutions</t>
+          <t>accH4=Credit and Lending</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>HIF</t>
+          <t>Global Trade Solutions</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>accH4=HIF</t>
+          <t>accH4=Global Trade Solutions</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CMA Net</t>
+          <t>HIF</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>accH4=CMA Net</t>
+          <t>accH4=HIF</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Other Revenue</t>
+          <t>CMA Net</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>accH4=Other Revenue</t>
+          <t>accH4=CMA Net</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Fee and other income</t>
+          <t>Other Revenue</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>income=Fee and other income</t>
+          <t>accH4=Other Revenue</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ECLs (ex Notables)</t>
+          <t>Fee and other income</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>accH3=ECLs (ex Notables)</t>
+          <t>income=Fee and other income</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Direct Costs (ex VP)</t>
+          <t>ECLs (ex Notables)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>accH4=Direct Costs (ex VP)</t>
+          <t>accH3=ECLs (ex Notables)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Variable Pay (VP)</t>
+          <t>Direct Costs (ex VP)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>accH4=Variable Pay (VP)</t>
+          <t>accH4=Direct Costs (ex VP)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Total Operating Expenses (ex Notables)</t>
+          <t>Variable Pay (VP)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>accH3=Total Operating Expenses (ex Notables)</t>
+          <t>accH4=Variable Pay (VP)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PBT (ex Notables)</t>
+          <t>Total Operating Expenses (ex Notables)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>accH2=PBT (ex Notables)</t>
+          <t>accH3=Total Operating Expenses (ex Notables)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PBT (Reported)</t>
+          <t>PBT (ex Notables)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>accH1=PBT (Reported)</t>
+          <t>accH2=PBT (ex Notables)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Customer Deposits (PE)</t>
+          <t>PBT (Reported)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>accH2=o/w Customer Deposits (PE)</t>
+          <t>accH1=PBT (Reported)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Loans and Advances to Customers (PE)</t>
+          <t>Customer Deposits (PE)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>accH2=o/w Loans and Advances to Customers (PE)</t>
+          <t>accH2=o/w Customer Deposits (PE)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>Loans and Advances to Customers (PE)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>accH2=o/w Loans and Advances to Customers (PE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>Total RWAs</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>accH1=Total RWAs</t>
         </is>

--- a/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
@@ -15,11 +15,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Views" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Labels" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metrics" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commentary" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ProductHierarchy" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AccountHierarchy" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CountryHierarchy" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CommentaryTemplates" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Definitions" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commentary" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ProductHierarchy" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AccountHierarchy" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CountryHierarchy" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CommentaryTemplates" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1454,6 +1455,173 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NII carried the half. Deposit margin held better than the plan assumed as the pass-through on time deposits was slower than expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Net Fee Income was the softer line. Investment activity thinned after the March rally and brokerage volumes have not come back, though the recurring wealth fee base is unchanged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Deposits ended the half broadly flat. The migration from current accounts into time deposits continued at much the same pace as the first quarter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Loans grew on mortgage completions that had been sitting in the pipeline since February.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Cards spend was seasonally strong in June but the balance build is behind where the plan had it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Insurance new business held up against a soft market, helped by the bancassurance push in the second quarter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Trading Income was flat and is not expected to move materially in the second half.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>The half closed ahead of plan on revenue, with costs the watch item into the second half.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Financial Summary</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Rates and FX carried the half; deposit margin narrowed broadly as planned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Markets and Securities Services</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Rates and FX led the half while Custody stayed soft.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Global Trade Solutions</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Drawdowns slipped into July - timing, not demand. The pipeline is intact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>June closes the half ahead of plan on revenue and behind on costs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Global Payments Solutions</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Payments volumes held up well; liquidity margin thinner as rates came off.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3507,7 +3675,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4892,7 +5060,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7065,7 +7233,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8629,7 +8797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -8668,356 +8836,322 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Banking NII</t>
+          <t>Fees and Other Income</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>micaL2=Revenue; micaL3!=Net Insurance Revenue</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>IWPB</t>
+          <t>accH3=Fees and Other Income</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Banking NII</t>
+          <t>PBT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>accH3=Banking NII</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>CIB</t>
+          <t>accH1=PBT ex Notables</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Fees and Other Income</t>
+          <t>Direct Cost ex VP, CC, GT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>accH3=Fees and Other Income</t>
+          <t>accH3=Direct Cost ex VP, CC, GT</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PBT</t>
+          <t>Variable Pay ex CC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>accH1=PBT ex Notables</t>
+          <t>accH3=Variable Pay ex CC</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Direct Cost ex VP, CC, GT</t>
+          <t>Indirect Costs</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>accH3=Direct Cost ex VP, CC, GT</t>
+          <t>accH3=Indirect Costs</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Variable Pay ex CC</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>accH3=Variable Pay ex CC</t>
+          <t>accH2=Operating Expenses</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Indirect Costs</t>
+          <t>ECL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>accH3=Indirect Costs</t>
+          <t>accH2=ECLs</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Deposits</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>accH2=Operating Expenses</t>
+          <t>accH2=Deposits</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ECL</t>
+          <t>Loans and Advances</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>accH2=ECLs</t>
+          <t>accH2=Loans and Advances</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Deposits</t>
+          <t>Total Revenue (ex Notables)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>accH2=Deposits</t>
+          <t>accH3=Total Revenue (ex Notables)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Loans and Advances</t>
+          <t>MSS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>accH2=Loans and Advances</t>
+          <t>accH4=MSS</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Total Revenue (ex Notables)</t>
+          <t>Global Payments Solutions</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>accH3=Total Revenue (ex Notables)</t>
+          <t>accH4=Global Payments Solutions</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MSS</t>
+          <t>Credit and Lending</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>accH4=MSS</t>
+          <t>accH4=Credit and Lending</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Global Payments Solutions</t>
+          <t>Global Trade Solutions</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>accH4=Global Payments Solutions</t>
+          <t>accH4=Global Trade Solutions</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Credit and Lending</t>
+          <t>HIF</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>accH4=Credit and Lending</t>
+          <t>accH4=HIF</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Global Trade Solutions</t>
+          <t>CMA Net</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>accH4=Global Trade Solutions</t>
+          <t>accH4=CMA Net</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HIF</t>
+          <t>Other Revenue</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>accH4=HIF</t>
+          <t>accH4=Other Revenue</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CMA Net</t>
+          <t>Fee and other income</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>accH4=CMA Net</t>
+          <t>income=Fee and other income</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Other Revenue</t>
+          <t>ECLs (ex Notables)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>accH4=Other Revenue</t>
+          <t>accH3=ECLs (ex Notables)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Fee and other income</t>
+          <t>Direct Costs (ex VP)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>income=Fee and other income</t>
+          <t>accH4=Direct Costs (ex VP)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ECLs (ex Notables)</t>
+          <t>Variable Pay (VP)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>accH3=ECLs (ex Notables)</t>
+          <t>accH4=Variable Pay (VP)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Direct Costs (ex VP)</t>
+          <t>Total Operating Expenses (ex Notables)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>accH4=Direct Costs (ex VP)</t>
+          <t>accH3=Total Operating Expenses (ex Notables)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Variable Pay (VP)</t>
+          <t>PBT (ex Notables)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>accH4=Variable Pay (VP)</t>
+          <t>accH2=PBT (ex Notables)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Total Operating Expenses (ex Notables)</t>
+          <t>PBT (Reported)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>accH3=Total Operating Expenses (ex Notables)</t>
+          <t>accH1=PBT (Reported)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PBT (ex Notables)</t>
+          <t>Customer Deposits (PE)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>accH2=PBT (ex Notables)</t>
+          <t>accH2=o/w Customer Deposits (PE)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PBT (Reported)</t>
+          <t>Loans and Advances to Customers (PE)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>accH1=PBT (Reported)</t>
+          <t>accH2=o/w Loans and Advances to Customers (PE)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Customer Deposits (PE)</t>
+          <t>Total RWAs</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
-        <is>
-          <t>accH2=o/w Customer Deposits (PE)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Loans and Advances to Customers (PE)</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>accH2=o/w Loans and Advances to Customers (PE)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Total RWAs</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
         <is>
           <t>accH1=Total RWAs</t>
         </is>
@@ -9034,159 +9168,107 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>Calculation</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Line</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Text</t>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Include</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NII carried the half. Deposit margin held better than the plan assumed as the pass-through on time deposits was slower than expected.</t>
+          <t>&lt;One calculation per group of rows: each row is one component. Column A: the calculation name (put it on the grid with a "+" row on the Tiles tab). Column B: which business this definition belongs to (IWPB, CIB, ...) — blank covers every business that wrote none. Column C: a line of the driller by name, from any MICA or hierarchy level. Column D: + includes the line, − carves it out. This tab is the lineage: what you read here is exactly what the tile computes.&gt;</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Net Fee Income was the softer line. Investment activity thinned after the March rally and brokerage volumes have not come back, though the recurring wealth fee base is unchanged.</t>
+          <t>Banking NII</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>+</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Deposits ended the half broadly flat. The migration from current accounts into time deposits continued at much the same pace as the first quarter.</t>
+          <t>Banking NII</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Net Insurance Revenue</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>−</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Loans grew on mortgage completions that had been sitting in the pipeline since February.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Cards spend was seasonally strong in June but the balance build is behind where the plan had it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Insurance new business held up against a soft market, helped by the bancassurance push in the second quarter.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Trading Income was flat and is not expected to move materially in the second half.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>The half closed ahead of plan on revenue, with costs the watch item into the second half.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Financial Summary</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Rates and FX carried the half; deposit margin narrowed broadly as planned.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Markets and Securities Services</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Rates and FX led the half while Custody stayed soft.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Global Trade Solutions</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Drawdowns slipped into July - timing, not demand. The pipeline is intact.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Summary</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>June closes the half ahead of plan on revenue and behind on costs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Global Payments Solutions</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Payments volumes held up well; liquidity margin thinner as rates came off.</t>
+          <t>Banking NII</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Banking NII</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>+</t>
         </is>
       </c>
     </row>

--- a/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
@@ -7425,7 +7425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -7453,18 +7453,6 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>One row per tile. Column A: the tile name as it reads on the Summary — or a pattern like cost.* for a family. Column B: Y shows, N hides (hidden tiles stay one click away behind "Show parked tiles"; a tab of only-Y rows shows JUST those), and + ADDS a line the grid does not carry — resolved from the Metrics sheet or any MICA level, so "Banking NII | +" puts Banking NII on the grid without touching the rest. Column C (optional): the line or lines this tile nets in — e.g. Revenue nets with "Other Revenue"; "-" stops a netting the page would otherwise make. Delete all rows to show the default grid.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Banking NII</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>+</t>
         </is>
       </c>
     </row>
@@ -9168,13 +9156,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9198,11 +9188,21 @@
           <t>Include</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>MICA level</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Tile</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>&lt;One calculation per group of rows: each row is one component. Column A: the calculation name (put it on the grid with a "+" row on the Tiles tab). Column B: which business this definition belongs to (IWPB, CIB, ...) — blank covers every business that wrote none. Column C: a line of the driller by name, from any MICA or hierarchy level. Column D: + includes the line, − carves it out. This tab is the lineage: what you read here is exactly what the tile computes.&gt;</t>
+          <t>&lt;One calculation per group of rows: each row is one component. Column A: the calculation name — it follows through onto the tiles and the commentary by itself (put N in the Tile column to keep it a definition only). Column B: which business this definition belongs to (IWPB, CIB, ...) — blank covers every business that wrote none. Column C: a line of the driller by name. Column D: + includes the line, − carves it out. Column E: which level the line lives at — L1..L4 for MICA, or a hierarchy key like accH3 — so a name that exists at two levels is never guessed; blank searches every level. This tab is the lineage: what you read here is exactly what the tile computes.&gt;</t>
         </is>
       </c>
     </row>
@@ -9227,6 +9227,12 @@
           <t>+</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9249,6 +9255,12 @@
           <t>−</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9271,6 +9283,12 @@
           <t>+</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>accH3</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
@@ -7425,7 +7425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -7453,6 +7453,114 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>One row per tile. Column A: the tile name as it reads on the Summary — or a pattern like cost.* for a family. Column B: Y shows, N hides (hidden tiles stay one click away behind "Show parked tiles"; a tab of only-Y rows shows JUST those), and + ADDS a line the grid does not carry — resolved from the Metrics sheet or any MICA level, so "Banking NII | +" puts Banking NII on the grid without touching the rest. Column C (optional): the line or lines this tile nets in — e.g. Revenue nets with "Other Revenue"; "-" stops a netting the page would otherwise make. Delete all rows to show the default grid.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>PBT</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Banking NII</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Total Direct Cost</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Total Indirect Costs (incl InterCo)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Expected credit losses</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Share of Profit.*</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Customer Deposits</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Loan and Advances</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -9232,7 +9340,6 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9260,7 +9367,6 @@
           <t>L3</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9288,7 +9394,6 @@
           <t>accH3</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
@@ -5066,7 +5066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E81"/>
+  <dimension ref="A1:E87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7225,6 +7225,160 @@
       <c r="D81" t="inlineStr">
         <is>
           <t>Holdings</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>G3</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>G4</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Corp Centre</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Corp Centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>G6</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Corp Centre</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Corporate Centre</t>
         </is>
       </c>
     </row>

--- a/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
@@ -7352,7 +7352,6 @@
           <t>Global</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
           <t>Corp Centre</t>
@@ -7375,7 +7374,6 @@
           <t>Global</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
           <t>Corporate Centre</t>
@@ -8852,7 +8850,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Period &amp; RAG</t>
+          <t>Period</t>
         </is>
       </c>
     </row>

--- a/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
@@ -21,6 +21,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AccountHierarchy" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CountryHierarchy" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CommentaryTemplates" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -46,7 +47,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -56,6 +57,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DB0011"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="009E1B32"/>
       </patternFill>
     </fill>
   </fills>
@@ -71,10 +77,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -7571,6 +7578,826 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Dim</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Dim2</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Value2</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Statement</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>From</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>To</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ME crisis — Gulf rate cuts</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>MICA Level 3</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NII - Net Interest Income</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>MENAT</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>pl</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>-8</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>AUG</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ME crisis — EGP devaluation</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>pl</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>-35</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>SEP</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ME crisis — deposit flight</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>MICA Level 2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Customer Deposits</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>bs</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>-15</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>SEP</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ME crisis — deposit flight</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>MICA Level 2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Customer Deposits</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Turkiye</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>bs</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>-15</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>SEP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ME crisis — deposit flight</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>MICA Level 3</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NII - Net Interest Income</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>pl</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>-9</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>SEP</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ME crisis — deposit flight</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>MICA Level 3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NII - Net Interest Income</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Turkiye</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>pl</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>-9</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>SEP</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ME crisis — Gulf inflows (upside)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>MICA Level 2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Customer Deposits</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>bs</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>8</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>SEP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ME crisis — Gulf inflows (upside)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>MICA Level 2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Customer Deposits</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>bs</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>8</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>SEP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ME crisis — Gulf inflows (upside)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>MICA Level 3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NII - Net Interest Income</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>pl</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>5</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>SEP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ME crisis — Gulf inflows (upside)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>MICA Level 3</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NII - Net Interest Income</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>pl</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>5</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>SEP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ME crisis — trade disruption</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>MICA Level 3</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Net Fee Income</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>MENAT</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>pl</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>-10</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>AUG</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ME crisis — trade disruption</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MICA Level 3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NII - Net Interest Income</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>MENAT</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>pl</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>AUG</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ME crisis — counter-case (oil spike)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>MICA Level 3</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NII - Net Interest Income</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>MENAT</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>pl</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>6</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>JUL</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ME crisis — counter-case (oil spike)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>MICA Level 3</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NII - Net Interest Income</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>pl</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>JUL</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ME crisis — counter-case (oil spike)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>MICA Level 2</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Expected credit losses</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>MENAT</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>pl</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>10</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>JUL</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
@@ -7584,7 +7584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -7717,8 +7717,6 @@
           <t>Egypt</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>pl</t>
@@ -8388,6 +8386,558 @@
         </is>
       </c>
       <c r="J16" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Macro — global rate cuts</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>MICA Level 3</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NII - Net Interest Income</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>pl</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>AUG</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Macro — China hard landing</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>MICA Level 3</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NII - Net Interest Income</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>pl</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>SEP</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Macro — China hard landing</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>MICA Level 3</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Net Fee Income</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>pl</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>SEP</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Macro — China hard landing</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>MICA Level 2</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Expected credit losses</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>pl</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>12</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>SEP</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Macro — US/Europe recession</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>MICA Level 3</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NII - Net Interest Income</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Americas and Europe</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>pl</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>AUG</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Macro — US/Europe recession</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>MICA Level 3</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Net Fee Income</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Americas and Europe</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>pl</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>AUG</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Macro — US/Europe recession</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>MICA Level 2</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Expected credit losses</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Americas and Europe</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>pl</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>15</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>AUG</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Macro — markets rally (upside)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>MICA Level 3</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Net Fee Income</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>pl</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>8</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>AUG</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Macro — markets rally (upside)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>MICA Level 2</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Customer Deposits</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>bs</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>3</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>AUG</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Macro — stagflation</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>MICA Level 3</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NII - Net Interest Income</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>pl</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>3</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>AUG</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Macro — stagflation</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>MICA Level 2</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Total Direct Cost</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>pl</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>4</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>AUG</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Macro — stagflation</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>MICA Level 2</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Expected credit losses</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>pl</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>8</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>AUG</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
         <is>
           <t>DEC</t>
         </is>

--- a/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
@@ -21,7 +21,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AccountHierarchy" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CountryHierarchy" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CommentaryTemplates" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simulations" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -7584,7 +7584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -7602,7 +7602,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Scenario</t>
+          <t>Simulation</t>
         </is>
       </c>
       <c r="B1" s="3" t="inlineStr">
@@ -8407,8 +8407,6 @@
           <t>NII - Net Interest Income</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>pl</t>
@@ -8749,8 +8747,6 @@
           <t>Net Fee Income</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>pl</t>
@@ -8791,8 +8787,6 @@
           <t>Customer Deposits</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>bs</t>
@@ -8833,8 +8827,6 @@
           <t>NII - Net Interest Income</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>pl</t>
@@ -8875,8 +8867,6 @@
           <t>Total Direct Cost</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>pl</t>
@@ -8917,8 +8907,6 @@
           <t>Expected credit losses</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>pl</t>
@@ -8938,6 +8926,274 @@
         </is>
       </c>
       <c r="J28" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Cost — pay review (wage inflation)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>MICA Level 3</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Direct Costs</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>pl</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>4</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>AUG</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Cost — variable pay true-up</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>MICA Level 3</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Variable Pay</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>pl</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>12</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>OCT</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Cost — savings programme</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>MICA Level 2</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Total Direct Cost</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>pl</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>SEP</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Cost — indirect cost inflation</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>MICA Level 2</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Total Indirect Costs</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>pl</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>6</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>JUL</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Cost — offshoring footprint shift</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>MICA Level 3</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Direct Costs</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>pl</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>SEP</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Cost — offshoring footprint shift</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>MICA Level 3</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Direct Costs</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>pl</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>3</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>SEP</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
         <is>
           <t>DEC</t>
         </is>

--- a/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
@@ -7584,7 +7584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -7597,6 +7597,7 @@
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="6" customWidth="1" min="9" max="9"/>
     <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7650,6 +7651,11 @@
           <t>To</t>
         </is>
       </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7700,6 +7706,11 @@
           <t>DEC</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Geopolitical</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7740,6 +7751,11 @@
           <t>DEC</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Geopolitical</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7790,6 +7806,11 @@
           <t>DEC</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Geopolitical</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7840,6 +7861,11 @@
           <t>DEC</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Geopolitical</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7890,6 +7916,11 @@
           <t>DEC</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Geopolitical</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7940,6 +7971,11 @@
           <t>DEC</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Geopolitical</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7990,6 +8026,11 @@
           <t>DEC</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Geopolitical</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8040,6 +8081,11 @@
           <t>DEC</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Geopolitical</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8090,6 +8136,11 @@
           <t>DEC</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Geopolitical</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8140,6 +8191,11 @@
           <t>DEC</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Geopolitical</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8190,6 +8246,11 @@
           <t>DEC</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Geopolitical</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -8240,6 +8301,11 @@
           <t>DEC</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Geopolitical</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -8290,6 +8356,11 @@
           <t>DEC</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Geopolitical</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8340,6 +8411,11 @@
           <t>DEC</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Geopolitical</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -8390,6 +8466,11 @@
           <t>DEC</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Geopolitical</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8430,6 +8511,11 @@
           <t>DEC</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Macroeconomic</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -8480,6 +8566,11 @@
           <t>DEC</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Macroeconomic</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -8530,6 +8621,11 @@
           <t>DEC</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Macroeconomic</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -8580,6 +8676,11 @@
           <t>DEC</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Macroeconomic</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -8630,6 +8731,11 @@
           <t>DEC</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Macroeconomic</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -8680,6 +8786,11 @@
           <t>DEC</t>
         </is>
       </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Macroeconomic</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -8730,6 +8841,11 @@
           <t>DEC</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Macroeconomic</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -8770,6 +8886,11 @@
           <t>DEC</t>
         </is>
       </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Macroeconomic</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -8810,6 +8931,11 @@
           <t>DEC</t>
         </is>
       </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Macroeconomic</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -8850,6 +8976,11 @@
           <t>DEC</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Macroeconomic</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -8890,6 +9021,11 @@
           <t>DEC</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Macroeconomic</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -8930,6 +9066,11 @@
           <t>DEC</t>
         </is>
       </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Macroeconomic</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -8947,8 +9088,6 @@
           <t>Direct Costs</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>pl</t>
@@ -8972,6 +9111,11 @@
           <t>DEC</t>
         </is>
       </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -8989,8 +9133,6 @@
           <t>Variable Pay</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>pl</t>
@@ -9014,6 +9156,11 @@
           <t>DEC</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -9031,8 +9178,6 @@
           <t>Total Direct Cost</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>pl</t>
@@ -9056,6 +9201,11 @@
           <t>DEC</t>
         </is>
       </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -9073,8 +9223,6 @@
           <t>Total Indirect Costs</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>pl</t>
@@ -9098,6 +9246,11 @@
           <t>DEC</t>
         </is>
       </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -9148,6 +9301,11 @@
           <t>DEC</t>
         </is>
       </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -9196,6 +9354,11 @@
       <c r="J34" t="inlineStr">
         <is>
           <t>DEC</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Cost</t>
         </is>
       </c>
     </row>

--- a/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
@@ -10487,7 +10487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -10682,7 +10682,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Load new Driller</t>
+          <t>Ingest TM1 Extract</t>
         </is>
       </c>
     </row>
@@ -10827,6 +10827,30 @@
       <c r="B28" t="inlineStr">
         <is>
           <t>Executive decisions</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ingest_title</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Ingest TM1 Extract</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ingest_drop</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Drop the TM1 extract here</t>
         </is>
       </c>
     </row>

--- a/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B91"/>
+  <dimension ref="A1:B93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1449,6 +1449,26 @@
         <is>
           <t>revenue|income|\bfees?\b|\bnii\b|turnover|\bnnii\b</t>
         </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>tile_height</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>tile_min_width</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>236</v>
       </c>
     </row>
   </sheetData>

--- a/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
@@ -1458,7 +1458,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>124</v>
+        <v>150</v>
       </c>
     </row>
     <row r="93">
@@ -1468,7 +1468,7 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>236</v>
+        <v>252</v>
       </c>
     </row>
   </sheetData>

--- a/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
@@ -10507,7 +10507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -10871,6 +10871,30 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>Drop the TM1 extract here</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>nav_bizperf</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Business performance</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>nav_comall</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>All commentaries</t>
         </is>
       </c>
     </row>

--- a/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
@@ -10702,7 +10702,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ingest TM1 Extract</t>
+          <t>Ingest TM1 Data Extract</t>
         </is>
       </c>
     </row>
@@ -10858,7 +10858,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ingest TM1 Extract</t>
+          <t>Ingest TM1 Data Extract</t>
         </is>
       </c>
     </row>
@@ -10870,7 +10870,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Drop the TM1 extract here</t>
+          <t>Drop the TM1 data extract here</t>
         </is>
       </c>
     </row>

--- a/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
@@ -10507,20 +10507,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Key</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
@@ -10577,72 +10577,72 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>nav_table</t>
+          <t>nav_assist</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Data drill down</t>
+          <t>MI Assistant</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>nav_assist</t>
+          <t>nav_sim</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MI Assistant</t>
+          <t>Simulation Assistant</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>nav_sim</t>
+          <t>nav_fsum</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Simulation Assistant</t>
+          <t>Financial Summary</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>nav_fsum</t>
+          <t>nav_comall</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Financial Summary</t>
+          <t>All commentaries</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>sect_dashboards</t>
+          <t>nav_bizperf</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>KPI Dashboards</t>
+          <t>Business performance</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>sect_kpis</t>
+          <t>sect_dashboards</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>KPIs · MICA Level 2</t>
+          <t>KPI Dashboards</t>
         </is>
       </c>
     </row>
@@ -10673,31 +10673,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>sect_filters</t>
+          <t>sect_comtpl</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Filters — all columns</t>
+          <t>Commentary templates</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>sect_output</t>
+          <t>btn_newfile</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Output fields</t>
+          <t>Ingest TM1 Data Extract</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>btn_newfile</t>
+          <t>ingest_title</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -10709,12 +10709,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>sect_drivers</t>
+          <t>ingest_drop</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Drivers · AI commentary</t>
+          <t>Drop the TM1 data extract here</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>drv_hint</t>
+          <t>lbl_year</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Known business drivers — the AI weaves them into chart commentary wherever the line appears as a mover.</t>
+          <t>Year</t>
         </is>
       </c>
     </row>
@@ -10769,132 +10769,72 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>lbl_fc</t>
+          <t>lbl_varper</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Include forecast month</t>
+          <t>Variance period</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>lbl_tol</t>
+          <t>lbl_units</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>RAG tolerance</t>
+          <t>Units</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>lbl_varper</t>
+          <t>lbl_scope</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Variance period</t>
+          <t>Scope</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>lbl_units</t>
+          <t>lbl_tplpick</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Units</t>
+          <t>Active style</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>kpi_hint</t>
+          <t>dec_eyebrow</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Click a KPI to see its trajectory and commentary · drag one onto My dashboard to add a card</t>
+          <t>Decisions required</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>dec_eyebrow</t>
+          <t>dec_title</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Decisions required</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>dec_title</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
           <t>Executive decisions</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>ingest_title</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Ingest TM1 Data Extract</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>ingest_drop</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Drop the TM1 data extract here</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>nav_bizperf</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Business performance</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>nav_comall</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>All commentaries</t>
         </is>
       </c>
     </row>

--- a/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
@@ -22,6 +22,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CountryHierarchy" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CommentaryTemplates" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simulations" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rollup" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -9387,6 +9388,457 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="52" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Level</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Roll up</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Grain</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Match</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MICA Level 1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>PBT</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>P&amp;L</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>PBT|PBT ex Notables</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>The result equals its components</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>MICA Level 2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>P&amp;L</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>MICA Level 2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Total Direct Cost</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>P&amp;L</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Total Direct Cost|Direct Costs</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MICA Level 2</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Expected credit losses</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>P&amp;L</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Expected credit losses|ECL|ECLs</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MICA Level 2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Total Indirect Costs</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>P&amp;L</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Total Indirect Costs|Total Indirect Costs (incl InterCo)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>MICA Level 2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Customer Deposits</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Balance</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Customer Deposits|Deposits</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Closing position</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>MICA Level 2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Loan and Advances</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Balance</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Loan and Advances|Loans and Advances|Loans</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Closing position</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MICA Level 3</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Net Fee Income</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>As reported</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>P&amp;L</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Country, Region, Global, Group</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Net Fee Income|Fees</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Reported at each level — never added up from the level beneath</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MICA Level 2</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CER</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Ratio</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Country, Region, Global, Group</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>CER|Cost Efficiency Ratio</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>A ratio is never added; it is read at the level asked for</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MICA Level 2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Banking NII</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Memo</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>P&amp;L</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Banking NII</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Calculated in Definitions from Revenue less Net Insurance Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>MICA Level 3</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>o/w Litigation</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Memo</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>P&amp;L</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Litigation|o/w Litigation</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Disclosure only</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
@@ -9394,50 +9394,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="44" customWidth="1" min="6" max="6"/>
-    <col width="52" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="52" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Level</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Line</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Roll up</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Basis</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Grain</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Match</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -9466,15 +9472,20 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>US$m</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>All</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>PBT|PBT ex Notables</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>The result equals its components</t>
         </is>
@@ -9503,15 +9514,19 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>US$m</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>All</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9536,15 +9551,19 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>US$m</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>All</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Total Direct Cost|Direct Costs</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9569,15 +9588,19 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>US$m</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>All</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Expected credit losses|ECL|ECLs</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -9602,15 +9625,19 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>US$m</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>All</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Total Indirect Costs|Total Indirect Costs (incl InterCo)</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9635,15 +9662,20 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>US$bn</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>All</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Customer Deposits|Deposits</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Closing position</t>
         </is>
@@ -9672,15 +9704,20 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>US$bn</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>All</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Loan and Advances|Loans and Advances|Loans</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>Closing position</t>
         </is>
@@ -9709,15 +9746,20 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>US$m</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>Country, Region, Global, Group</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Net Fee Income|Fees</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Reported at each level — never added up from the level beneath</t>
         </is>
@@ -9744,17 +9786,18 @@
           <t>Ratio</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
         <is>
           <t>Country, Region, Global, Group</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>CER|Cost Efficiency Ratio</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>A ratio is never added; it is read at the level asked for</t>
         </is>
@@ -9783,15 +9826,20 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>US$m</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>All</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Banking NII</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Calculated in Definitions from Revenue less Net Insurance Revenue</t>
         </is>
@@ -9820,15 +9868,20 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>US$m</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>All</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>Litigation|o/w Litigation</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>Disclosure only</t>
         </is>

--- a/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
@@ -9786,7 +9786,6 @@
           <t>Ratio</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>Country, Region, Global, Group</t>
@@ -11729,11 +11728,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
@@ -78,11 +78,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -9897,25 +9898,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Tile</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Show</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Nets with</t>
         </is>
@@ -9924,7 +9926,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>One row per tile. Column A: the tile name as it reads on the Summary — or a pattern like cost.* for a family. Column B: Y shows, N hides (hidden tiles stay one click away behind "Show parked tiles"; a tab of only-Y rows shows JUST those), and + ADDS a line the grid does not carry — resolved from the Metrics sheet or any MICA level, so "Banking NII | +" puts Banking NII on the grid without touching the rest. Column C (optional): the line or lines this tile nets in — e.g. Revenue nets with "Other Revenue"; "-" stops a netting the page would otherwise make. Delete all rows to show the default grid.</t>
+          <t>One row per tile. Column A: the line's name (a pattern like 'Share of Profit.*' also works). Column B: Y shows it, N parks it where the reader can bring it back, X (or Never) keeps it off the page altogether. '+' adds a line that is not a tile by default. Column C nets another line into this one.</t>
         </is>
       </c>
     </row>
@@ -10035,6 +10037,19 @@
           <t>Y</t>
         </is>
       </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>&lt;a line you never want on the page&gt;</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
@@ -10049,7 +10049,6 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11739,15 +11738,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11778,6 +11778,11 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Product Level</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Tile</t>
         </is>
       </c>
@@ -11785,9 +11790,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>&lt;One calculation per group of rows: each row is one component. Column A: the calculation name — it follows through onto the tiles and the commentary by itself (put N in the Tile column to keep it a definition only). Column B: which business this definition belongs to (IWPB, CIB, ...) — blank covers every business that wrote none. Column C: a line of the driller by name. Column D: + includes the line, − carves it out. Column E: which level the line lives at — L1..L4 for MICA, or a hierarchy key like accH3 — so a name that exists at two levels is never guessed; blank searches every level. This tab is the lineage: what you read here is exactly what the tile computes.&gt;</t>
-        </is>
-      </c>
+          <t>&lt;One calculation per group of rows. Include: + adds the line, − carves it out, / makes it the denominator of a ratio. MICA level names the column the line lives in (L3, MICA_Level_3). Product Level optionally qualifies it: a bare column name lets the line be found there too, "Product_Level_7 = Wealth" restricts it to that value.&gt;</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -11802,7 +11813,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>NII - Net Interest Income</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -11812,9 +11823,11 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>L2</t>
-        </is>
-      </c>
+          <t>MICA_Level_3</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11834,14 +11847,16 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>L3</t>
-        </is>
-      </c>
+          <t>MICA_Level_3</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11869,6 +11884,8 @@
           <t>accH3</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
@@ -11790,7 +11790,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>&lt;One calculation per group of rows. Include: + adds the line, − carves it out, / makes it the denominator of a ratio. MICA level names the column the line lives in (L3, MICA_Level_3). Product Level optionally qualifies it: a bare column name lets the line be found there too, "Product_Level_7 = Wealth" restricts it to that value.&gt;</t>
+          <t>&lt;One calculation per group of rows. Include: + adds the line, − takes it out, / makes it the denominator of a ratio. MICA level names the column the line lives in (L3, MICA_Level_3, Product_Level_7, accH3). Product Level optionally qualifies it: a bare column name lets the line be found there too, "Product_Level_7 = Wealth" restricts it to that value. A line taken out is removed from the selection where it sits inside the base, and subtracted where it does not.&gt;</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11813,7 +11813,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NII - Net Interest Income</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -11823,7 +11823,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MICA_Level_3</t>
+          <t>MICA_Level_2</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>

--- a/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/Group_dashboard_config_pack.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B93"/>
+  <dimension ref="A1:B95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1356,121 +1356,145 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>%|\bbps\b|\brote\b|\bcer\b|\bratio\b|headcount|\bfte\b|\bcount\b</t>
+          <t>%|\bbps\b|\brote\b|\bcer\b|\bratio\b</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>commentary_driver_floor</t>
+          <t>count_patterns</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>headcount|\bfte\b|\bcounts?\b|customers|\bnos\b|\bnumber\b|\bheads\b</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>commentary_driver_cover</t>
+          <t>commentary_driver_floor</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>commentary_max_notes</t>
+          <t>commentary_driver_cover</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>80</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>fsum_notes</t>
+          <t>commentary_max_notes</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>fsum_note_lines</t>
+          <t>fsum_notes</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>auto</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>tile_visible</t>
+          <t>fsum_note_lines</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>tile_net</t>
+          <t>tile_visible</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>tile_net_auto</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Y</t>
+          <t>tile_net</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>revenue_patterns</t>
+          <t>tile_net_auto</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>revenue|income|\bfees?\b|\bnii\b|turnover|\bnnii\b</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>tile_height</t>
-        </is>
-      </c>
-      <c r="B92" t="n">
-        <v>150</v>
+          <t>revenue_patterns</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>revenue|income|\bfees?\b|\bnii\b|turnover|\bnnii\b</t>
+        </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
+          <t>tile_height</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
           <t>tile_min_width</t>
         </is>
       </c>
-      <c r="B93" t="n">
+      <c r="B94" t="n">
         <v>252</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>tile_unit_label</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -11793,12 +11817,6 @@
           <t>&lt;One calculation per group of rows. Include: + adds the line, − takes it out, / makes it the denominator of a ratio. MICA level names the column the line lives in (L3, MICA_Level_3, Product_Level_7, accH3). Product Level optionally qualifies it: a bare column name lets the line be found there too, "Product_Level_7 = Wealth" restricts it to that value. A line taken out is removed from the selection where it sits inside the base, and subtracted where it does not.&gt;</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -11826,8 +11844,6 @@
           <t>MICA_Level_2</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11855,8 +11871,6 @@
           <t>MICA_Level_3</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11884,8 +11898,6 @@
           <t>accH3</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
